--- a/EndResult/200m Fri.xlsx
+++ b/EndResult/200m Fri.xlsx
@@ -537,12 +537,12 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Christoffer Solberg Jørgensen</t>
+          <t>Simen Dahl Stensaas</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>1.56,08</t>
+          <t>1.56,09</t>
         </is>
       </c>
       <c r="C4" t="n">
@@ -572,12 +572,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Simen Dahl Stensaas</t>
+          <t>Christoffer Solberg Jørgensen</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>1.56,09</t>
+          <t>1.56,08</t>
         </is>
       </c>
       <c r="C5" t="n">
@@ -1269,23 +1269,27 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Merete Fuglem Løvberg</t>
+          <t>Maria Erikovna Alvestad</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2.05,23</t>
+          <t>2.04,53</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>682</v>
+        <v>695</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>26.11.1983</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr"/>
+          <t>26.10.2025</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>Stavanger</t>
+        </is>
+      </c>
       <c r="F2" t="inlineStr">
         <is>
           <t>25m</t>
@@ -1300,27 +1304,23 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Maria Erikovna Alvestad</t>
+          <t>Merete Fuglem Løvberg</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2.08,62</t>
+          <t>2.05,23</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>630</v>
+        <v>682</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>26.04.2025</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>Trondheim</t>
-        </is>
-      </c>
+          <t>26.11.1983</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr"/>
       <c r="F3" t="inlineStr">
         <is>
           <t>25m</t>

--- a/EndResult/200m Fri.xlsx
+++ b/EndResult/200m Fri.xlsx
@@ -537,12 +537,12 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Simen Dahl Stensaas</t>
+          <t>Christoffer Solberg Jørgensen</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>1.56,09</t>
+          <t>1.56,08</t>
         </is>
       </c>
       <c r="C4" t="n">
@@ -572,12 +572,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Christoffer Solberg Jørgensen</t>
+          <t>Simen Dahl Stensaas</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>1.56,08</t>
+          <t>1.56,09</t>
         </is>
       </c>
       <c r="C5" t="n">
@@ -1183,25 +1183,25 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Tor Arne Hegvik</t>
+          <t>Thomas Trøite</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2.06,70</t>
+          <t>2.05,62</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>521</v>
+        <v>535</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>28.04.2007</t>
+          <t>22.03.2026</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Namsos</t>
+          <t>Oslo</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
